--- a/aggregator/documentation/important-links.xlsx
+++ b/aggregator/documentation/important-links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCHAUH21\work\workspace_lab\parent\aggregator\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6F4BE5-E822-49B0-9AEC-D90E0E0BAE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1DDF61-CE0D-4167-B40F-4CA0EA83E449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="34776" windowHeight="21096" activeTab="3" xr2:uid="{0B1A7EAF-F057-DA43-849F-8C9C7ABA47AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="34776" windowHeight="21096" xr2:uid="{0B1A7EAF-F057-DA43-849F-8C9C7ABA47AB}"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
   <si>
     <t>https://www.youtube.com/@Javatechie/videos</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>Design Patterns</t>
+  </si>
+  <si>
+    <t>https://github.com/shabbirdwd53/design_patterns/tree/main/factory</t>
   </si>
 </sst>
 </file>
@@ -649,7 +652,7 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.796875" customWidth="1"/>
+    <col min="1" max="1" width="75.69921875" customWidth="1"/>
     <col min="2" max="2" width="30.296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -668,6 +671,11 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>69</v>
@@ -682,6 +690,7 @@
     <hyperlink ref="A2" r:id="rId2" xr:uid="{C0931E14-B596-DA48-B53B-7FDB10BD5468}"/>
     <hyperlink ref="A3" r:id="rId3" xr:uid="{568B5860-5A33-894B-A5F5-03F9957E966E}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{4464D912-28A9-4ECA-9C86-AC5F4777BF36}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{D44E0CBB-ACDB-4C72-B221-2AEF27A1DCB9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
